--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783312</v>
+        <v>121783333</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R2" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R3" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R2" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783312</v>
+        <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R4" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783312</v>
+        <v>121783304</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -770,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R3" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +907,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R4" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,6 +990,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R2" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783333</v>
+        <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R3" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783333</v>
+        <v>121783304</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>56569</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R2" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +823,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R3" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R3" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -877,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783312</v>
+        <v>121783333</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,38 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R4" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B2" t="n">
-        <v>56569</v>
+        <v>57365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R2" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -788,7 +788,7 @@
         <v>121783312</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783333</v>
+        <v>121783304</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R4" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B2" t="n">
-        <v>57365</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R2" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783312</v>
+        <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
+        <v>56577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783304</v>
+        <v>121783333</v>
       </c>
       <c r="B4" t="n">
-        <v>56577</v>
+        <v>57365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R4" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1006,6 +1006,254 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122111033</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57734</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 12684-2023, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>296835</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6530115</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 2 ex</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122111403</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92021</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 12684-2023, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>296825</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6530090</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-12-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 mycel. Tydlig mycelfilt.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122111033</v>
+        <v>122111403</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>92065</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,35 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296835</v>
+        <v>296825</v>
       </c>
       <c r="R5" t="n">
-        <v>6530115</v>
+        <v>6530090</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,24 +1093,14 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 2 ex</t>
+          <t>1 mycel. Tydlig mycelfilt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122111403</v>
+        <v>122111033</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>57744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296825</v>
+        <v>296835</v>
       </c>
       <c r="R6" t="n">
-        <v>6530090</v>
+        <v>6530115</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,14 +1213,24 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 mycel. Tydlig mycelfilt.</t>
+          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1239,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122111403</v>
+        <v>122111033</v>
       </c>
       <c r="B5" t="n">
-        <v>92065</v>
+        <v>57744</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,34 +1025,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296825</v>
+        <v>296835</v>
       </c>
       <c r="R5" t="n">
-        <v>6530090</v>
+        <v>6530115</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,14 +1094,24 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 mycel. Tydlig mycelfilt.</t>
+          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1120,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122111033</v>
+        <v>122111403</v>
       </c>
       <c r="B6" t="n">
-        <v>57744</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,35 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296835</v>
+        <v>296825</v>
       </c>
       <c r="R6" t="n">
-        <v>6530115</v>
+        <v>6530090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,24 +1222,14 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 2 ex</t>
+          <t>1 mycel. Tydlig mycelfilt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,6 +1238,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122111033</v>
+        <v>122111403</v>
       </c>
       <c r="B5" t="n">
-        <v>57744</v>
+        <v>92077</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,35 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1061,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296835</v>
+        <v>296825</v>
       </c>
       <c r="R5" t="n">
-        <v>6530115</v>
+        <v>6530090</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,24 +1093,14 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 2 ex</t>
+          <t>1 mycel. Tydlig mycelfilt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,6 +1109,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122111403</v>
+        <v>122111033</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296825</v>
+        <v>296835</v>
       </c>
       <c r="R6" t="n">
-        <v>6530090</v>
+        <v>6530115</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,14 +1213,24 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 mycel. Tydlig mycelfilt.</t>
+          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1239,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>122111403</v>
       </c>
       <c r="B5" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1012,7 +1012,7 @@
         <v>122111403</v>
       </c>
       <c r="B5" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,11 +1026,6 @@
       </c>
       <c r="E5" t="n">
         <v>4364</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1145,11 +1140,6 @@
       </c>
       <c r="E6" t="n">
         <v>103015</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122111403</v>
+        <v>122111033</v>
       </c>
       <c r="B5" t="n">
-        <v>92087</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,29 +1025,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1055,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296825</v>
+        <v>296835</v>
       </c>
       <c r="R5" t="n">
-        <v>6530090</v>
+        <v>6530115</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,14 +1094,24 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 mycel. Tydlig mycelfilt.</t>
+          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1120,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1123,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122111033</v>
+        <v>122111403</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>92100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,30 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1189,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296835</v>
+        <v>296825</v>
       </c>
       <c r="R6" t="n">
-        <v>6530115</v>
+        <v>6530090</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,24 +1222,14 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 2 ex</t>
+          <t>1 mycel. Tydlig mycelfilt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,6 +1238,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -788,11 +788,11 @@
         <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>56594</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>56594</v>
+        <v>56688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>121783304</v>
       </c>
       <c r="B3" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121783333</v>
+        <v>121783312</v>
       </c>
       <c r="B2" t="n">
-        <v>57374</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296885</v>
+        <v>296820</v>
       </c>
       <c r="R2" t="n">
-        <v>6530079</v>
+        <v>6530061</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,47 +784,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121783304</v>
+        <v>122111403</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296820</v>
+        <v>296825</v>
       </c>
       <c r="R3" t="n">
-        <v>6530061</v>
+        <v>6530090</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,74 +868,72 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 mycel. Tydlig mycelfilt.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121783312</v>
+        <v>121783333</v>
       </c>
       <c r="B4" t="n">
-        <v>92039</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296820</v>
+        <v>296885</v>
       </c>
       <c r="R4" t="n">
-        <v>6530061</v>
+        <v>6530079</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,15 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122111033</v>
+        <v>121783304</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,33 +1014,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296835</v>
+        <v>296820</v>
       </c>
       <c r="R5" t="n">
-        <v>6530115</v>
+        <v>6530061</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,24 +1079,9 @@
           <t>2024-12-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,27 +1096,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122111403</v>
+        <v>122111033</v>
       </c>
       <c r="B6" t="n">
-        <v>92100</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,34 +1119,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,13 +1155,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296825</v>
+        <v>296835</v>
       </c>
       <c r="R6" t="n">
-        <v>6530090</v>
+        <v>6530115</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,14 +1188,24 @@
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-29</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 mycel. Tydlig mycelfilt.</t>
+          <t>Minst 2 ex</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,7 +1214,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 12684-2023 artfynd.xlsx
+++ b/artfynd/A 12684-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121783312</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122111403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121783333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121783304</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,8 +1254,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122111033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>